--- a/DataAnalysis/TryingToPackStuffBetter/PreprocessingRTandDIM/CS/0.05/Results.xlsx
+++ b/DataAnalysis/TryingToPackStuffBetter/PreprocessingRTandDIM/CS/0.05/Results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\TryingToPackStuffBetter\PreprocessingRTandDIM\CS\0.05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B59159F-A9ED-4060-825E-7B1EA2CEA083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FEE7531-413C-4BA8-9482-AB082BBB8106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -162,8 +162,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -486,34 +487,34 @@
       <c r="B3" t="s">
         <v>3</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>24.555555555555557</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>2.0531141657924863</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>17.888888888888889</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>3.4980153103025557</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>25.222222222222221</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>1.9702650695894817</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="1">
         <v>22.555555555555557</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="1">
         <v>1.3176156917368251</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>4.7777777777777777</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="1">
         <v>2.5792979234236939</v>
       </c>
     </row>
@@ -521,34 +522,34 @@
       <c r="B4" t="s">
         <v>2</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>26.166666666666668</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>2.753785273643051</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>20</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <v>2.2912878474779199</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>24.333333333333332</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>1.8929694486000914</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="1">
         <v>23.5</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="1">
         <v>2.179449471770337</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>3.5</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="1">
         <v>1</v>
       </c>
     </row>
@@ -556,34 +557,34 @@
       <c r="B5" t="s">
         <v>26</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>24.111111111111111</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>2.2329601678290438</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>19.722222222222221</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <v>5.380004130522992</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>22.722222222222221</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>2.2653795365113645</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="1">
         <v>22.185185185185183</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="1">
         <v>1.6403007101605136</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>4.0185185185185182</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="1">
         <v>1.7939799880519469</v>
       </c>
     </row>
@@ -591,34 +592,34 @@
       <c r="B6" t="s">
         <v>28</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="1">
         <v>23.9</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
         <v>3.1898275815473092</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <v>18.5</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="1">
         <v>2.8504385627478448</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>24.2</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>2.4647515087732472</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="1">
         <v>22.2</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="1">
         <v>2.340465290872261</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>3.7</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="1">
         <v>2.0662634015159931</v>
       </c>
     </row>
